--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -564,295 +564,295 @@
     <t>Fabricación estructura proveedor externo OT 4340,Generacion OC Fabricación Externa OT 4340</t>
   </si>
   <si>
+    <t>1215166243334606</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340,Fabricación Externa  OT 4340</t>
+  </si>
+  <si>
+    <t>1215165982859560</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo OT 4340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  OT 4340,Control de calidad fabricación externa  OT 4340,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215165982859577</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  OT 4340</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215165982859589</t>
+  </si>
+  <si>
+    <t>Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340,Generación OC Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166433442059</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340,Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243346004</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado OT 4340</t>
+  </si>
+  <si>
+    <t>1215166243396278</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215166243396290</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166433496869</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215166041791429</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215166041791446</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos motor proveedor OT 4340</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215165982964919</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado OT 4340,Propuesta Fabricación externa  OT 4340,propuesta Corte Laser OT 4340,Propuesta Corte plasma  OT 4340,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243476961</t>
+  </si>
+  <si>
+    <t>1215165982983044</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215165982983056</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215165983005052</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215165983005064</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215166329404944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166041891869</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215166041891891</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215165982799201</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215166243533900</t>
+  </si>
+  <si>
+    <t>1215166243533917</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215166433625222</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
+  </si>
+  <si>
+    <t>1215166433625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215166243563189</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>1215166329517772</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,check planos</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Armado</t>
+  </si>
+  <si>
+    <t>1215166041950163</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215166041950180</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
+    <t>1215165983080450</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215166329573409</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Bodega:</t>
+  </si>
+  <si>
+    <t>1215166329573431</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Bodega:</t>
+  </si>
+  <si>
+    <t>1215166433753017</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215166329638303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215166243334606</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340,Fabricación Externa  OT 4340</t>
-  </si>
-  <si>
-    <t>1215165982859560</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo OT 4340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  OT 4340,Control de calidad fabricación externa  OT 4340,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215165982859577</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  OT 4340</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215165982859589</t>
-  </si>
-  <si>
-    <t>Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340,Generación OC Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166433442059</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340,Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243346004</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado OT 4340</t>
-  </si>
-  <si>
-    <t>1215166243396278</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215166243396290</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166433496869</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215166041791429</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215166041791446</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Planos motor proveedor OT 4340</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215165982964919</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado OT 4340,Propuesta Fabricación externa  OT 4340,propuesta Corte Laser OT 4340,Propuesta Corte plasma  OT 4340,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243476961</t>
-  </si>
-  <si>
-    <t>1215165982983044</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215165982983056</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215165983005052</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215165983005064</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215166329404944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166041891869</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215166041891891</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215165982799201</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215166243533900</t>
-  </si>
-  <si>
-    <t>1215166243533917</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,Armado,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215166433625222</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
-  </si>
-  <si>
-    <t>1215166433625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215166243563189</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>1215166329517772</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,check planos</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Armado</t>
-  </si>
-  <si>
-    <t>1215166041950163</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215166041950180</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>1215165983080450</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215166329573409</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,Bodega:</t>
-  </si>
-  <si>
-    <t>1215166329573431</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Bodega:</t>
-  </si>
-  <si>
-    <t>1215166433753017</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215166329638303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
   </si>
   <si>
     <t>1215166243719413</t>
@@ -3827,7 +3827,7 @@
         <v>46190.64487847222</v>
       </c>
       <c r="D39" s="8">
-        <v>46274.147179050924</v>
+        <v>46282.15889856481</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>146</v>
@@ -3871,8 +3871,8 @@
       <c r="R39" s="8">
         <v>46281</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>150</v>
+      <c r="S39" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3928,7 +3928,7 @@
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3950,7 +3950,7 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
@@ -3983,7 +3983,7 @@
         <v>89</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -4005,16 +4005,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
+      <c r="H42" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4035,7 +4035,7 @@
         <v>146</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4060,7 +4060,7 @@
         <v>46254.168984062504</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4090,7 +4090,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4113,7 +4113,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4152,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4180,7 +4180,7 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4207,13 +4207,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4235,7 +4235,7 @@
         <v>46240.716379722224</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4259,7 +4259,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4288,16 +4288,16 @@
         <v>46250.128330694446</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4315,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4353,16 +4353,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4380,13 +4380,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4408,16 +4408,16 @@
         <v>46250.12945143519</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>173</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4435,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4473,16 +4473,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4500,13 +4500,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4534,10 +4534,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4555,13 +4555,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4593,16 +4593,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>177</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4623,7 +4623,7 @@
         <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>78</v>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4648,16 +4648,16 @@
         <v>46250.12991684028</v>
       </c>
       <c r="E53" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
+      <c r="H53" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4675,10 +4675,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4713,16 +4713,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>190</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4740,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4768,7 +4768,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4792,7 +4792,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4821,16 +4821,16 @@
         <v>46256.202002488426</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4848,13 +4848,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>135</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4874,7 +4874,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4886,16 +4886,16 @@
         <v>46260.206319432866</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4913,13 +4913,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4951,16 +4951,16 @@
         <v>46256.2020027199</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4978,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>143</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5004,7 +5004,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5016,16 +5016,16 @@
         <v>46260.2063193287</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5043,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5064,12 +5064,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5081,16 +5081,16 @@
         <v>46256.20200275463</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H60" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5108,13 +5108,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5146,16 +5146,16 @@
         <v>46260.20631930555</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5173,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5194,12 +5194,12 @@
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5211,7 +5211,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5235,7 +5235,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5252,7 +5252,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5264,16 +5264,16 @@
         <v>46269.174344178246</v>
       </c>
       <c r="E63" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="9" t="s">
+      <c r="H63" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5291,13 +5291,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5329,16 +5329,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5356,13 +5356,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="O64" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5384,16 +5384,16 @@
         <v>46274.16343969907</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5411,13 +5411,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5432,12 +5432,12 @@
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5449,16 +5449,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5476,13 +5476,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O66" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="P66" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="P66" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5492,7 +5492,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5504,16 +5504,16 @@
         <v>46276.14507925926</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>158</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>159</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5531,13 +5531,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5552,12 +5552,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5569,16 +5569,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5596,13 +5596,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5624,7 +5624,7 @@
         <v>46250.12706636574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5648,7 +5648,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5673,16 +5673,16 @@
         <v>46224.186405659726</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5700,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5726,7 +5726,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5738,16 +5738,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5765,13 +5765,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>103</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5791,7 +5791,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5803,16 +5803,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5830,13 +5830,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>121</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5856,7 +5856,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5868,16 +5868,16 @@
         <v>46275.13273378472</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>199</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>200</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5895,13 +5895,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5910,7 +5910,7 @@
         <v>46282</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>150</v>
+        <v>246</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>
@@ -6034,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6051,7 +6051,7 @@
         <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6136,7 +6136,7 @@
         <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>248</v>
@@ -6171,7 +6171,7 @@
         <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6376,7 +6376,7 @@
         <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>248</v>
@@ -6411,7 +6411,7 @@
         <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6496,7 +6496,7 @@
         <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>248</v>
@@ -6531,7 +6531,7 @@
         <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6561,7 +6561,7 @@
         <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>274</v>
@@ -6681,7 +6681,7 @@
         <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>279</v>
@@ -6824,7 +6824,7 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6909,7 +6909,7 @@
         <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>281</v>
@@ -6944,7 +6944,7 @@
         <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6974,7 +6974,7 @@
         <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>292</v>
@@ -7005,10 +7005,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7029,7 +7029,7 @@
         <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>281</v>
@@ -7047,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7064,16 +7064,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7094,7 +7094,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>296</v>
@@ -7125,10 +7125,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7149,7 +7149,7 @@
         <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>299</v>
@@ -7184,16 +7184,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7214,7 +7214,7 @@
         <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>298</v>

--- a/data/50001557 - ATACAMA KOZAN OT4340.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4340.xlsx
@@ -465,6 +465,9 @@
     <t>Generación OC motor OT 4340,Fabricación motor OT 4340,Planos motor proveedor OT 4340</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215166433395184</t>
   </si>
   <si>
@@ -850,9 +853,6 @@
   </si>
   <si>
     <t>Revestimiento,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215166243719413</t>
@@ -3217,7 +3217,7 @@
         <v>46182.67350289352</v>
       </c>
       <c r="D29" s="8">
-        <v>46200.81836952546</v>
+        <v>46283.147219189814</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3261,8 +3261,8 @@
       <c r="R29" s="8">
         <v>46290</v>
       </c>
-      <c r="S29" s="10" t="s">
-        <v>32</v>
+      <c r="S29" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" s="5">
         <v>46169.55833486111</v>
@@ -3285,7 +3285,7 @@
         <v>46195.69066259259</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3318,7 +3318,7 @@
         <v>66</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3334,7 +3334,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B31" s="8">
         <v>46169.5583402662</v>
@@ -3346,7 +3346,7 @@
         <v>46195.69066760417</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3376,10 +3376,10 @@
         <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3395,7 +3395,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B32" s="5">
         <v>46169.55834503472</v>
@@ -3407,7 +3407,7 @@
         <v>46195.6906680324</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3437,10 +3437,10 @@
         <v>115</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3456,7 +3456,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46169.55836335648</v>
@@ -3468,16 +3468,16 @@
         <v>46254.16898400463</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I33" s="8">
         <v>46241</v>
@@ -3498,7 +3498,7 @@
         <v>91</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>91</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5">
         <v>46169.558367986116</v>
@@ -3533,16 +3533,16 @@
         <v>46184.53245875</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I34" s="5">
         <v>46241</v>
@@ -3560,13 +3560,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3582,7 +3582,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B35" s="8">
         <v>46169.55837292824</v>
@@ -3594,16 +3594,16 @@
         <v>46184.532615856486</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I35" s="8">
         <v>46245</v>
@@ -3621,13 +3621,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B36" s="5">
         <v>46169.55837825232</v>
@@ -3655,16 +3655,16 @@
         <v>46254.16898402778</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I36" s="5">
         <v>46241</v>
@@ -3685,7 +3685,7 @@
         <v>91</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>26</v>
@@ -3708,7 +3708,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B37" s="8">
         <v>46169.558381979165</v>
@@ -3726,10 +3726,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I37" s="8">
         <v>46241</v>
@@ -3747,13 +3747,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>82</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46169.55838657408</v>
@@ -3775,16 +3775,16 @@
         <v>46184.53255631945</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I38" s="5">
         <v>46245</v>
@@ -3802,13 +3802,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>83</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46169.55839107639</v>
@@ -3830,16 +3830,16 @@
         <v>46282.15889856481</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I39" s="8">
         <v>46241</v>
@@ -3860,7 +3860,7 @@
         <v>91</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>26</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46169.55839478009</v>
@@ -3901,10 +3901,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I40" s="5">
         <v>46241</v>
@@ -3922,13 +3922,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>88</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B41" s="8">
         <v>46169.55839910879</v>
@@ -3950,16 +3950,16 @@
         <v>46195.70375376157</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -3977,13 +3977,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>89</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46169.55840355324</v>
@@ -4005,16 +4005,16 @@
         <v>46205.59994755787</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I42" s="5">
         <v>46281</v>
@@ -4032,10 +4032,10 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B43" s="8">
         <v>46169.55840677083</v>
@@ -4060,16 +4060,16 @@
         <v>46254.168984062504</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I43" s="8">
         <v>46241</v>
@@ -4090,7 +4090,7 @@
         <v>91</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4113,7 +4113,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B44" s="5">
         <v>46169.55841037037</v>
@@ -4131,10 +4131,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I44" s="5">
         <v>46241</v>
@@ -4152,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46169.558458217594</v>
@@ -4180,16 +4180,16 @@
         <v>46191.53698841435</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I45" s="8">
         <v>46245</v>
@@ -4207,13 +4207,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>86</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46169.5584643287</v>
@@ -4235,7 +4235,7 @@
         <v>46240.716379722224</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>25</v>
@@ -4259,7 +4259,7 @@
         <v>26</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B47" s="8">
         <v>46169.55846813657</v>
@@ -4288,16 +4288,16 @@
         <v>46250.128330694446</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4315,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="8">
         <v>46167</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B48" s="5">
         <v>46169.558472766206</v>
@@ -4353,16 +4353,16 @@
         <v>46181.72663056713</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4380,13 +4380,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4396,7 +4396,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46169.55849938658</v>
@@ -4408,16 +4408,16 @@
         <v>46250.12945143519</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I49" s="8">
         <v>46218</v>
@@ -4435,13 +4435,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q49" s="8">
         <v>46218</v>
@@ -4461,7 +4461,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46169.55850371528</v>
@@ -4473,16 +4473,16 @@
         <v>46195.690583055555</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46218</v>
@@ -4500,13 +4500,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4516,7 +4516,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46169.55853228009</v>
@@ -4534,10 +4534,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I51" s="8">
         <v>46238</v>
@@ -4555,13 +4555,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46238</v>
@@ -4581,7 +4581,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46169.55854641204</v>
@@ -4593,16 +4593,16 @@
         <v>46182.75984881945</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46238</v>
@@ -4623,7 +4623,7 @@
         <v>78</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>78</v>
@@ -4636,7 +4636,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B53" s="8">
         <v>46169.558565775464</v>
@@ -4648,16 +4648,16 @@
         <v>46250.12991684028</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I53" s="8">
         <v>46331</v>
@@ -4675,10 +4675,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46169.55856972223</v>
@@ -4713,16 +4713,16 @@
         <v>46211.86419394676</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I54" s="5">
         <v>46331</v>
@@ -4740,13 +4740,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46169.558586307874</v>
@@ -4768,7 +4768,7 @@
         <v>46198.597746307874</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>25</v>
@@ -4792,7 +4792,7 @@
         <v>26</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46169.55858945602</v>
@@ -4821,16 +4821,16 @@
         <v>46256.202002488426</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I56" s="5">
         <v>46254</v>
@@ -4848,13 +4848,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="5">
         <v>46254</v>
@@ -4874,7 +4874,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46169.55859488426</v>
@@ -4886,16 +4886,16 @@
         <v>46260.206319432866</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I57" s="8">
         <v>46258</v>
@@ -4913,13 +4913,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q57" s="8">
         <v>46258</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B58" s="5">
         <v>46169.55860118056</v>
@@ -4951,16 +4951,16 @@
         <v>46256.2020027199</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I58" s="5">
         <v>46254</v>
@@ -4978,13 +4978,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Q58" s="5">
         <v>46254</v>
@@ -5004,7 +5004,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46169.55860636574</v>
@@ -5016,16 +5016,16 @@
         <v>46260.2063193287</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I59" s="8">
         <v>46258</v>
@@ -5043,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q59" s="8">
         <v>46258</v>
@@ -5064,12 +5064,12 @@
         <v>1</v>
       </c>
       <c r="U59" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46169.558650127314</v>
@@ -5081,16 +5081,16 @@
         <v>46256.20200275463</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I60" s="5">
         <v>46254</v>
@@ -5108,13 +5108,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q60" s="5">
         <v>46254</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46169.55865608796</v>
@@ -5146,16 +5146,16 @@
         <v>46260.20631930555</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I61" s="8">
         <v>46258</v>
@@ -5173,13 +5173,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q61" s="8">
         <v>46258</v>
@@ -5194,12 +5194,12 @@
         <v>1</v>
       </c>
       <c r="U61" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46169.55866105324</v>
@@ -5211,7 +5211,7 @@
         <v>46198.68229049769</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>25</v>
@@ -5235,7 +5235,7 @@
         <v>26</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5252,7 +5252,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46169.55866469907</v>
@@ -5264,16 +5264,16 @@
         <v>46269.174344178246</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I63" s="8">
         <v>46260</v>
@@ -5291,13 +5291,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q63" s="8">
         <v>46260</v>
@@ -5317,7 +5317,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" s="5">
         <v>46169.55867099537</v>
@@ -5329,16 +5329,16 @@
         <v>46197.85936673611</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I64" s="5">
         <v>46260</v>
@@ -5356,13 +5356,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" s="8">
         <v>46169.558703518516</v>
@@ -5384,16 +5384,16 @@
         <v>46274.16343969907</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I65" s="8">
         <v>46269</v>
@@ -5411,13 +5411,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q65" s="8">
         <v>46269</v>
@@ -5432,12 +5432,12 @@
         <v>1</v>
       </c>
       <c r="U65" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B66" s="5">
         <v>46169.55870879629</v>
@@ -5449,16 +5449,16 @@
         <v>46197.85915420139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I66" s="5">
         <v>46269</v>
@@ -5476,13 +5476,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5492,7 +5492,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B67" s="8">
         <v>46169.558740625</v>
@@ -5504,16 +5504,16 @@
         <v>46276.14507925926</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I67" s="8">
         <v>46274</v>
@@ -5531,13 +5531,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q67" s="8">
         <v>46274</v>
@@ -5552,12 +5552,12 @@
         <v>1</v>
       </c>
       <c r="U67" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B68" s="5">
         <v>46169.558745243055</v>
@@ -5569,16 +5569,16 @@
         <v>46205.659588587965</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I68" s="5">
         <v>46274</v>
@@ -5596,13 +5596,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B69" s="8">
         <v>46169.55876947917</v>
@@ -5624,7 +5624,7 @@
         <v>46250.12706636574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>25</v>
@@ -5648,7 +5648,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>26</v>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
         <v>46169.55880633101</v>
@@ -5673,16 +5673,16 @@
         <v>46224.186405659726</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I70" s="5">
         <v>46220</v>
@@ -5700,13 +5700,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>112</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q70" s="5">
         <v>46220</v>
@@ -5726,7 +5726,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B71" s="8">
         <v>46169.5588177662</v>
@@ -5738,16 +5738,16 @@
         <v>46200.819831597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I71" s="8">
         <v>46325</v>
@@ -5765,13 +5765,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>103</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="8">
         <v>46325</v>
@@ -5791,7 +5791,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" s="5">
         <v>46169.55882295139</v>
@@ -5803,16 +5803,16 @@
         <v>46200.81928909722</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I72" s="5">
         <v>46293</v>
@@ -5830,13 +5830,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q72" s="5">
         <v>46293</v>
@@ -5856,7 +5856,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
         <v>46169.55882788195</v>
@@ -5865,19 +5865,19 @@
         <v>46211.70928436343</v>
       </c>
       <c r="D73" s="8">
-        <v>46275.13273378472</v>
+        <v>46283.15998347222</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I73" s="8">
         <v>46282</v>
@@ -5895,13 +5895,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q73" s="8">
         <v>46282</v>
@@ -5909,8 +5909,8 @@
       <c r="R73" s="8">
         <v>46282</v>
       </c>
-      <c r="S73" s="12" t="s">
-        <v>246</v>
+      <c r="S73" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>
@@ -6034,7 +6034,7 @@
         <v>1</v>
       </c>
       <c r="U75" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6051,7 +6051,7 @@
         <v>46223.57064498843</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6136,7 +6136,7 @@
         <v>248</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>248</v>
@@ -6171,7 +6171,7 @@
         <v>46223.57074214121</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6376,7 +6376,7 @@
         <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>248</v>
@@ -6411,7 +6411,7 @@
         <v>46223.835960763885</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6496,7 +6496,7 @@
         <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>248</v>
@@ -6531,7 +6531,7 @@
         <v>46223.57092783565</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6561,7 +6561,7 @@
         <v>272</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>274</v>
@@ -6681,7 +6681,7 @@
         <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>279</v>
@@ -6824,7 +6824,7 @@
         <v>46211.700054201385</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6909,7 +6909,7 @@
         <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>281</v>
@@ -6944,7 +6944,7 @@
         <v>46223.57147459491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6974,7 +6974,7 @@
         <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>292</v>
@@ -7005,10 +7005,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I92" s="5">
         <v>46337</v>
@@ -7029,7 +7029,7 @@
         <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>281</v>
@@ -7047,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7064,16 +7064,16 @@
         <v>46211.830942650464</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I93" s="8">
         <v>46337</v>
@@ -7094,7 +7094,7 @@
         <v>294</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>296</v>
@@ -7125,10 +7125,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46338</v>
@@ -7149,7 +7149,7 @@
         <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>299</v>
@@ -7184,16 +7184,16 @@
         <v>46211.863992280094</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46338</v>
@@ -7214,7 +7214,7 @@
         <v>298</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>298</v>
